--- a/04_DESIGN_TABLES/DesignTable_6500.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6500.xlsx
@@ -3372,24 +3372,56 @@
           <t>6500-04-06-FG</t>
         </is>
       </c>
+      <c r="B46" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.297</v>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
           <t>6500-04-06-FG</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>7/16-20 (male JIC) x 9/16-18 (female JIC swivel)</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6500-04-06 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6500-04-06 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied; 2026-10-09 (left out of batch 15, staged): LEG_M@DRIVE: OMi Items row 1913 L 1 Size = 1.05; LEG_M5@DRIVE: OMi Items row 1913 M 2 Size = 1.25; LEG_M10@DRIVE: OMi Items row 1913 M 1 Size = 0.88; HEXB@HEX: OMi Items row 1913 Nut Hex 1 = 0.688; Y@REF: OMi Items row 1913 Hex Flat = 0.562; D1@BORE: OMi Items row 1913 Side 1 ID = 0.172; D2@BORE: OMi Items row 1913 Side 2 ID = 0.297; THDMAJ_A@DRIVE: 7/16-20 -&gt; 0.4375 (end library); THDMAJ_B@DRIVE: 9/16-18 -&gt; 0.5625 (end library) [user 2026-09-25: OMi dims &gt; Air-Way; user 2026-10-08: no size from Brennan alone -&gt; OMi stands, ASSUMED]; pairing: OMi L 1 = male JIC leg (catalog M), M 2 = swivel-nut face (M6), M 1 = swivel nose / seat (M4), Hex Flat = body hex, Nut Hex 1 = swivel nut hex, Side 1 / 2 ID = bores of ends 1 / 2 (batch-15 pairing, Brennan TFA p34 letters)</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6500-04-06 dims are NOT assumed; confirm before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6500-04-06 dims are NOT assumed; confirm before modelling | RESOLVED 2026-10-09 (staged): this part's own sizes from OMi WebsitePartsInfo2026 Items row 1913 - ASSUMED (one source). It was held in batch 15 because the Brennan TFA catalog prints other values for it; under the 2026-10-08 ruling the catalog (= OMi's source) is evidence only and OMi stands. Catalog print for the record: TFA-p034-t01: TUBE O.D. 1/4, B1 SAE 37Deg 7/16-20, B2 SAE 37Deg 9/16-18, B1 DRILL 0.172, B2 DRILL 0.297, M LGTH 1.05, M4 LGTH 0.87, M6 LGTH 1.25, C HEX 0.688, Y FLATS 0.562</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -3478,24 +3510,56 @@
           <t>6500-12-08-FG</t>
         </is>
       </c>
+      <c r="B48" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.391</v>
+      </c>
       <c r="K48" t="inlineStr">
         <is>
           <t>6500-12-08-FG</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>1 1/16-12 (male JIC) x 3/4-16 (female JIC swivel)</t>
+        </is>
+      </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6500-12-08 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6500-12-08 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied; 2026-10-09 (left out of batch 15, staged): LEG_M@DRIVE: OMi Items row 1925 L 1 Size = 1.66; LEG_M5@DRIVE: OMi Items row 1925 M 2 Size = 1.55; LEG_M10@DRIVE: OMi Items row 1925 M 1 Size = 1.13; HEXB@HEX: OMi Items row 1925 Nut Hex 1 = 0.875; Y@REF: OMi Items row 1925 Hex Flat = 1.062; D1@BORE: OMi Items row 1925 Side 1 ID = 0.609; D2@BORE: OMi Items row 1925 Side 2 ID = 0.391; THDMAJ_A@DRIVE: 1 1/16-12 -&gt; 1.0625 (end library); THDMAJ_B@DRIVE: 3/4-16 -&gt; 0.75 (end library) [user 2026-09-25: OMi dims &gt; Air-Way; user 2026-10-08: no size from Brennan alone -&gt; OMi stands, ASSUMED]; pairing: OMi L 1 = male JIC leg (catalog M), M 2 = swivel-nut face (M6), M 1 = swivel nose / seat (M4), Hex Flat = body hex, Nut Hex 1 = swivel nut hex, Side 1 / 2 ID = bores of ends 1 / 2 (batch-15 pairing, Brennan TFA p34 letters)</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6500-12-08 dims are NOT assumed; confirm before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6500-12-08 dims are NOT assumed; confirm before modelling | RESOLVED 2026-10-09 (staged): this part's own sizes from OMi WebsitePartsInfo2026 Items row 1925 - ASSUMED (one source). It was held in batch 15 because the Brennan TFA catalog prints other values for it; under the 2026-10-08 ruling the catalog (= OMi's source) is evidence only and OMi stands. Catalog print for the record: TFA-p034-t01: TUBE O.D. 3/4, B1 SAE 37Deg 1-1/16-12, B2 SAE 37Deg 3/4-16, B1 DRILL 0.609, B2 DRILL 0.391, M LGTH 1.660, M4 LGTH 1.120, M6 LGTH 1.550, C HEX 0.875, Y FLATS 1.062</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -3515,24 +3579,56 @@
           <t>6500-12-16-FG</t>
         </is>
       </c>
+      <c r="B49" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="C49" t="n">
+        <v>2</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.844</v>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
           <t>6500-12-16-FG</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>1 1/16-12 (male JIC) x 1 5/16-12 (female JIC swivel)</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6500-12-16 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6500-12-16 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied; 2026-10-09 (left out of batch 15, staged): LEG_M@DRIVE: OMi Items row 1927 L 1 Size = 1.76; LEG_M5@DRIVE: OMi Items row 1927 M 2 Size = 2.00; LEG_M10@DRIVE: OMi Items row 1927 M 1 Size = 1.41; HEXB@HEX: OMi Items row 1927 Nut Hex 1 = 1.500; Y@REF: OMi Items row 1927 Hex Flat = 1.312; D1@BORE: OMi Items row 1927 Side 1 ID = 0.609; D2@BORE: OMi Items row 1927 Side 2 ID = 0.844; THDMAJ_A@DRIVE: 1 1/16-12 -&gt; 1.0625 (end library); THDMAJ_B@DRIVE: 1 5/16-12 -&gt; 1.3125 (end library) [user 2026-09-25: OMi dims &gt; Air-Way; user 2026-10-08: no size from Brennan alone -&gt; OMi stands, ASSUMED]; pairing: OMi L 1 = male JIC leg (catalog M), M 2 = swivel-nut face (M6), M 1 = swivel nose / seat (M4), Hex Flat = body hex, Nut Hex 1 = swivel nut hex, Side 1 / 2 ID = bores of ends 1 / 2 (batch-15 pairing, Brennan TFA p34 letters)</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6500-12-16 dims are NOT assumed; confirm before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6500-12-16 dims are NOT assumed; confirm before modelling | RESOLVED 2026-10-09 (staged): this part's own sizes from OMi WebsitePartsInfo2026 Items row 1927 - ASSUMED (one source). It was held in batch 15 because the Brennan TFA catalog prints other values for it; under the 2026-10-08 ruling the catalog (= OMi's source) is evidence only and OMi stands. Catalog print for the record: TFA-p034-t01: TUBE O.D. 3/4, B1 SAE 37Deg 1-1/16-12, B2 SAE 37Deg 1-5/16-12, B1 DRILL 0.609, B2 DRILL 0.844, M LGTH 1.81, M4 LGTH 1.40, M6 LGTH 2.00, C HEX 1.500, Y FLATS 1.312</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -3552,24 +3648,56 @@
           <t>6500-16-12-FG</t>
         </is>
       </c>
+      <c r="B50" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.609</v>
+      </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>6500-16-12-FG</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>1 5/16-12 (male JIC) x 1 1/16-12 (female JIC swivel)</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6500-16-12 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 6500-16-12 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied; 2026-10-09 (left out of batch 15, staged): LEG_M@DRIVE: OMi Items row 1928 L 1 Size = 1.81; LEG_M5@DRIVE: OMi Items row 1928 M 2 Size = 1.95; LEG_M10@DRIVE: OMi Items row 1928 M 1 Size = 1.39; HEXB@HEX: OMi Items row 1928 Nut Hex 1 = 1.250; Y@REF: OMi Items row 1928 Hex Flat = 1.312; D1@BORE: OMi Items row 1928 Side 1 ID = 0.844; D2@BORE: OMi Items row 1928 Side 2 ID = 0.609; THDMAJ_A@DRIVE: 1 5/16-12 -&gt; 1.3125 (end library); THDMAJ_B@DRIVE: 1 1/16-12 -&gt; 1.0625 (end library) [user 2026-09-25: OMi dims &gt; Air-Way; user 2026-10-08: no size from Brennan alone -&gt; OMi stands, ASSUMED]; pairing: OMi L 1 = male JIC leg (catalog M), M 2 = swivel-nut face (M6), M 1 = swivel nose / seat (M4), Hex Flat = body hex, Nut Hex 1 = swivel nut hex, Side 1 / 2 ID = bores of ends 1 / 2 (batch-15 pairing, Brennan TFA p34 letters)</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6500-16-12 dims are NOT assumed; confirm before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 6500-16-12 dims are NOT assumed; confirm before modelling | RESOLVED 2026-10-09 (staged): this part's own sizes from OMi WebsitePartsInfo2026 Items row 1928 - ASSUMED (one source). It was held in batch 15 because the Brennan TFA catalog prints other values for it; under the 2026-10-08 ruling the catalog (= OMi's source) is evidence only and OMi stands. Catalog print for the record: TFA-p034-t01: TUBE O.D. 1, B1 SAE 37Deg 1-5/16-12, B2 SAE 37Deg 1-1/16-12, B1 DRILL 0.844, B2 DRILL 0.609, M LGTH 1.81, M4 LGTH 1.34, M6 LGTH 1.91, C HEX 1.250, Y FLATS 1.312</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">

--- a/04_DESIGN_TABLES/DesignTable_6500.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6500.xlsx
@@ -909,7 +909,7 @@
         <v>1.06</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>0.63</v>
@@ -946,12 +946,12 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1)</t>
+          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1); LEG_M10@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1914 = 0.68 (table had 0.69) [user 2026-10-18 A19]</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>BLOCKED: female-JIC swivel nut internal geometry UNPUBLISHED (nut thread depth, nose, sleeve seat) - measure a Brennan 6500 STEP | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat still MISSING</t>
+          <t>BLOCKED: female-JIC swivel nut internal geometry UNPUBLISHED (nut thread depth, nose, sleeve seat) - measure a Brennan 6500 STEP | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat still MISSING | A19 (user 2026-10-18, group 2 settled): LEG_M10@DRIVE 0.69 -&gt; OMi 0.68 (Items!N1914, M113)</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>BLOCKED: female-JIC swivel nut internal geometry UNPUBLISHED (nut thread depth, nose, sleeve seat) - measure a Brennan 6500 STEP | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat still MISSING</t>
+          <t>BLOCKED: female-JIC swivel nut internal geometry UNPUBLISHED (nut thread depth, nose, sleeve seat) - measure a Brennan 6500 STEP | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat still MISSING | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on LEG_M10@DRIVE=0.96~0.96; LEG_M5@DRIVE=1.38~1.38; LEG_M@DRIVE=1.14~1.14; Y@REF=0.75~0.750; HEXB@HEX=0.88~0.875; D1@BORE=0.3~0.297; D2@BORE=0.39~0.391</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1433,10 +1433,10 @@
         <v>1.25</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>0.6899999999999999</v>
@@ -1478,12 +1478,17 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>BLOCKED: female-JIC swivel nut internal geometry UNPUBLISHED (nut thread depth, nose, sleeve seat) - measure a Brennan 6500 STEP | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat still MISSING | DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
+          <t>BLOCKED: female-JIC swivel nut internal geometry UNPUBLISHED (nut thread depth, nose, sleeve seat) - measure a Brennan 6500 STEP | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat still MISSING | DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p034-t01: agrees on LEG_M@DRIVE, HEXB@HEX, Y@REF, D1@BORE, D2@BORE | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): LEG_M5@DRIVE 1.33 -&gt; 1.28 | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): LEG_M10@DRIVE 0.95 -&gt; 0.91 | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): $PRP@DataStatus VERIFIED -&gt; ASSUMED</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>6500-08-06-FG</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1601,7 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>VERIFIED-LEGS</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -1606,12 +1611,17 @@
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>BLOCKED: female-JIC swivel nut internal geometry UNPUBLISHED (nut thread depth, nose, sleeve seat) - measure a Brennan 6500 STEP | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat still MISSING | DROP: no matching OMi SKU in catalog feed (2026-09-23)</t>
+          <t>BLOCKED: female-JIC swivel nut internal geometry UNPUBLISHED (nut thread depth, nose, sleeve seat) - measure a Brennan 6500 STEP | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat still MISSING | DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p034-t01: agrees on LEG_M@DRIVE, HEXB@HEX, Y@REF, D1@BORE, D2@BORE</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>DROP</t>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>6500-08-08-FG</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1734,7 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -1734,7 +1744,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>BLOCKED: female-JIC swivel nut internal geometry UNPUBLISHED (nut thread depth, nose, sleeve seat) - measure a Brennan 6500 STEP | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat still MISSING</t>
+          <t>BLOCKED: female-JIC swivel nut internal geometry UNPUBLISHED (nut thread depth, nose, sleeve seat) - measure a Brennan 6500 STEP | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat still MISSING | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on LEG_M10@DRIVE=1.12~1.12; LEG_M5@DRIVE=1.62~1.62; LEG_M@DRIVE=1.33~1.33; Y@REF=0.88~0.875; HEXB@HEX=1~1.000; D1@BORE=0.39~0.391; D2@BORE=0.48~0.484</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -1990,7 +2000,7 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -2000,7 +2010,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>BLOCKED: female-JIC swivel nut internal geometry UNPUBLISHED (nut thread depth, nose, sleeve seat) - measure a Brennan 6500 STEP | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat still MISSING</t>
+          <t>BLOCKED: female-JIC swivel nut internal geometry UNPUBLISHED (nut thread depth, nose, sleeve seat) - measure a Brennan 6500 STEP | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat still MISSING | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on LEG_M10@DRIVE=1.09~1.09; LEG_M5@DRIVE=1.51~1.51; LEG_M@DRIVE=1.45~1.45; Y@REF=0.88~0.875; HEXB@HEX=0.88~0.875; D1@BORE=0.48~0.484; D2@BORE=0.39~0.391</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2224,7 +2234,7 @@
         <v>1.75</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>1.25</v>
@@ -2261,12 +2271,12 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1)</t>
+          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1); LEG_M10@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1924 = 1.18 (table had 1.19) [user 2026-10-18 A19]</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>BLOCKED: female-JIC swivel nut internal geometry UNPUBLISHED (nut thread depth, nose, sleeve seat) - measure a Brennan 6500 STEP | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat still MISSING</t>
+          <t>BLOCKED: female-JIC swivel nut internal geometry UNPUBLISHED (nut thread depth, nose, sleeve seat) - measure a Brennan 6500 STEP | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat still MISSING | A19 (user 2026-10-18, group 2 settled): LEG_M10@DRIVE 1.19 -&gt; OMi 1.18 (Items!N1924, M113)</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2549,7 +2559,7 @@
         <v>1.75</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>1.25</v>
@@ -2586,12 +2596,12 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1)</t>
+          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1); LEG_M10@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1926 = 1.18 (table had 1.19) [user 2026-10-18 A19]</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>BLOCKED: female-JIC swivel nut internal geometry UNPUBLISHED (nut thread depth, nose, sleeve seat) - measure a Brennan 6500 STEP | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat still MISSING</t>
+          <t>BLOCKED: female-JIC swivel nut internal geometry UNPUBLISHED (nut thread depth, nose, sleeve seat) - measure a Brennan 6500 STEP | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat still MISSING | A19 (user 2026-10-18, group 2 settled): LEG_M10@DRIVE 1.19 -&gt; OMi 1.18 (Items!N1926, M113)</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -2906,7 +2916,7 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -2916,7 +2926,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>legs differ from MS51521: AW M=1.81/M5=2.0 vs MS 1.8/2.0; BLOCKED: female-JIC swivel nut internal geometry UNPUBLISHED (nut thread depth, nose, sleeve seat) - measure a Brennan 6500 STEP | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat still MISSING</t>
+          <t>legs differ from MS51521: AW M=1.81/M5=2.0 vs MS 1.8/2.0; BLOCKED: female-JIC swivel nut internal geometry UNPUBLISHED (nut thread depth, nose, sleeve seat) - measure a Brennan 6500 STEP | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat still MISSING | A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on LEG_M10@DRIVE=1.41~1.41; LEG_M5@DRIVE=2~2.00; LEG_M@DRIVE=1.81~1.81; Y@REF=1.31~1.312; HEXB@HEX=1.5~1.500; D1@BORE=0.84~0.844; D2@BORE=0.84~0.844</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">

--- a/04_DESIGN_TABLES/DesignTable_6500.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6500.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="NutRef_MS51531D" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NutRef_MS51531D" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -909,7 +909,7 @@
         <v>1.06</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>0.63</v>
@@ -946,12 +946,12 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1); LEG_M10@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1914 = 0.68 (table had 0.69) [user 2026-10-18 A19]</t>
+          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1); LEG_M10@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1914 = 0.68 (table had 0.69) [user 2026-10-18 A19]; LEG_M10@DRIVE: Air-Way 0.69 (log (no Air-Way raw extract in the repo); OMi file / Brennan 0.68) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>BLOCKED: female-JIC swivel nut internal geometry UNPUBLISHED (nut thread depth, nose, sleeve seat) - measure a Brennan 6500 STEP | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat still MISSING | A19 (user 2026-10-18, group 2 settled): LEG_M10@DRIVE 0.69 -&gt; OMi 0.68 (Items!N1914, M113)</t>
+          <t>BLOCKED: female-JIC swivel nut internal geometry UNPUBLISHED (nut thread depth, nose, sleeve seat) - measure a Brennan 6500 STEP | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat still MISSING | A19 (user 2026-10-18, group 2 settled): LEG_M10@DRIVE 0.69 -&gt; OMi 0.68 (Items!N1914, M113) | 2026-10-20 Air-Way first: LEG_M10@DRIVE OMi/Brennan 0.68 -&gt; Air-Way 0.69</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1433,10 +1433,10 @@
         <v>1.25</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>0.6899999999999999</v>
@@ -1468,17 +1468,17 @@
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1)</t>
+          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1); LEG_M5@DRIVE: Air-Way 1.33 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.28) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; LEG_M10@DRIVE: Air-Way 0.95 (log (no Air-Way raw extract in the repo); OMi file / Brennan 0.91) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>BLOCKED: female-JIC swivel nut internal geometry UNPUBLISHED (nut thread depth, nose, sleeve seat) - measure a Brennan 6500 STEP | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat still MISSING | DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p034-t01: agrees on LEG_M@DRIVE, HEXB@HEX, Y@REF, D1@BORE, D2@BORE | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): LEG_M5@DRIVE 1.33 -&gt; 1.28 | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): LEG_M10@DRIVE 0.95 -&gt; 0.91 | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): $PRP@DataStatus VERIFIED -&gt; ASSUMED</t>
+          <t>BLOCKED: female-JIC swivel nut internal geometry UNPUBLISHED (nut thread depth, nose, sleeve seat) - measure a Brennan 6500 STEP | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat still MISSING | DROP: no matching OMi SKU in catalog feed (2026-09-23) | 2026-10-16: BUILD - the DROP above is void: OMi sells this part, the 2026-09-23 crawl had dropped its SKU | Brennan TFA TFA-p034-t01: agrees on LEG_M@DRIVE, HEXB@HEX, Y@REF, D1@BORE, D2@BORE | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): LEG_M5@DRIVE 1.33 -&gt; 1.28 | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): LEG_M10@DRIVE 0.95 -&gt; 0.91 | A19-style (user 2026-10-18 'yes, apply the 7 pending OMi values'): $PRP@DataStatus VERIFIED -&gt; ASSUMED | 2026-10-20 Air-Way first: LEG_M5@DRIVE OMi/Brennan 1.28 -&gt; Air-Way 1.33 | 2026-10-20 Air-Way first: LEG_M10@DRIVE OMi/Brennan 0.91 -&gt; Air-Way 0.95</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1841,7 +1841,7 @@
         <v>1.25</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>1.062</v>
+        <v>1.13</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>0.75</v>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R1921 Hex Flat = 1.062 (table had 1.13) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
+          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1); Y@REF: OMi WebsitePartsInfo2026.xlsx Items!R1921 Hex Flat = 1.062 (table had 1.13) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; Y@REF: Air-Way 1.13 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.062) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>BLOCKED: female-JIC swivel nut internal geometry UNPUBLISHED (nut thread depth, nose, sleeve seat) - measure a Brennan 6500 STEP | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat still MISSING</t>
+          <t>BLOCKED: female-JIC swivel nut internal geometry UNPUBLISHED (nut thread depth, nose, sleeve seat) - measure a Brennan 6500 STEP | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat still MISSING | 2026-10-20 Air-Way first: Y@REF OMi/Brennan 1.062 -&gt; Air-Way 1.13</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2234,7 +2234,7 @@
         <v>1.75</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>1.25</v>
@@ -2271,12 +2271,12 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1); LEG_M10@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1924 = 1.18 (table had 1.19) [user 2026-10-18 A19]</t>
+          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1); LEG_M10@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1924 = 1.18 (table had 1.19) [user 2026-10-18 A19]; LEG_M10@DRIVE: Air-Way 1.19 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.18) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>BLOCKED: female-JIC swivel nut internal geometry UNPUBLISHED (nut thread depth, nose, sleeve seat) - measure a Brennan 6500 STEP | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat still MISSING | A19 (user 2026-10-18, group 2 settled): LEG_M10@DRIVE 1.19 -&gt; OMi 1.18 (Items!N1924, M113)</t>
+          <t>BLOCKED: female-JIC swivel nut internal geometry UNPUBLISHED (nut thread depth, nose, sleeve seat) - measure a Brennan 6500 STEP | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat still MISSING | A19 (user 2026-10-18, group 2 settled): LEG_M10@DRIVE 1.19 -&gt; OMi 1.18 (Items!N1924, M113) | 2026-10-20 Air-Way first: LEG_M10@DRIVE OMi/Brennan 1.18 -&gt; Air-Way 1.19</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2559,7 +2559,7 @@
         <v>1.75</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="E33" s="3" t="n">
         <v>1.25</v>
@@ -2596,12 +2596,12 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1); LEG_M10@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1926 = 1.18 (table had 1.19) [user 2026-10-18 A19]</t>
+          <t>Male JIC end VERIFIED (MS33656J); legs: Air-Way (MS51521D Amd1 corroborates matched-dash M/M1); LEG_M10@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!N1926 = 1.18 (table had 1.19) [user 2026-10-18 A19]; LEG_M10@DRIVE: Air-Way 1.19 (log (no Air-Way raw extract in the repo); OMi file / Brennan 1.18) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>BLOCKED: female-JIC swivel nut internal geometry UNPUBLISHED (nut thread depth, nose, sleeve seat) - measure a Brennan 6500 STEP | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat still MISSING | A19 (user 2026-10-18, group 2 settled): LEG_M10@DRIVE 1.19 -&gt; OMi 1.18 (Items!N1926, M113)</t>
+          <t>BLOCKED: female-JIC swivel nut internal geometry UNPUBLISHED (nut thread depth, nose, sleeve seat) - measure a Brennan 6500 STEP | 2026-09-15: nut ENVELOPE (hex, bore, lengths, thread depth) now available as standard-nut reference in sheet NutRef_MS51531D (MS51531D primary, AN818 cross-check) - Air-Way nut as sold NOT confirmed; internal seat still MISSING | A19 (user 2026-10-18, group 2 settled): LEG_M10@DRIVE 1.19 -&gt; OMi 1.18 (Items!N1926, M113) | 2026-10-20 Air-Way first: LEG_M10@DRIVE OMi/Brennan 1.18 -&gt; Air-Way 1.19</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
